--- a/data_VR3.xlsx
+++ b/data_VR3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y0808\search-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819D0126-CAE1-4571-AE2D-B0DB3C6D41C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2ACA4D-A4AC-4F98-9214-430B41FF289B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6970" yWindow="810" windowWidth="11560" windowHeight="10170" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="3" activeTab="5" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="9">
   <si>
     <t>table</t>
     <phoneticPr fontId="1"/>
@@ -49,6 +49,18 @@
   </si>
   <si>
     <t>P-LR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>p-42</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>p-21</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>p-38</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3292,6 +3304,12 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>28</v>
+      </c>
+      <c r="D2">
+        <v>56</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
@@ -3300,6 +3318,12 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>28</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
@@ -3308,6 +3332,12 @@
       <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>46</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
@@ -3316,6 +3346,12 @@
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5">
+        <v>60</v>
+      </c>
+      <c r="D5">
+        <v>45</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
@@ -3324,6 +3360,12 @@
       <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6">
+        <v>67</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
@@ -3332,6 +3374,12 @@
       <c r="B7">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>62</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
@@ -3340,6 +3388,12 @@
       <c r="B8">
         <v>7</v>
       </c>
+      <c r="C8">
+        <v>36</v>
+      </c>
+      <c r="D8">
+        <v>49</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
@@ -3348,6 +3402,12 @@
       <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9">
+        <v>33</v>
+      </c>
+      <c r="D9">
+        <v>52</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
@@ -3356,6 +3416,12 @@
       <c r="B10">
         <v>9</v>
       </c>
+      <c r="C10">
+        <v>59</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
@@ -3364,6 +3430,12 @@
       <c r="B11">
         <v>10</v>
       </c>
+      <c r="C11">
+        <v>18</v>
+      </c>
+      <c r="D11">
+        <v>31</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
@@ -3372,6 +3444,12 @@
       <c r="B12">
         <v>11</v>
       </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
@@ -3380,6 +3458,12 @@
       <c r="B13">
         <v>12</v>
       </c>
+      <c r="C13">
+        <v>37</v>
+      </c>
+      <c r="D13">
+        <v>55</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
@@ -3388,6 +3472,12 @@
       <c r="B14">
         <v>13</v>
       </c>
+      <c r="C14">
+        <v>48</v>
+      </c>
+      <c r="D14">
+        <v>26</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
@@ -3396,6 +3486,12 @@
       <c r="B15">
         <v>14</v>
       </c>
+      <c r="C15">
+        <v>26</v>
+      </c>
+      <c r="D15">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
@@ -3404,685 +3500,1201 @@
       <c r="B16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C16">
+        <v>45</v>
+      </c>
+      <c r="D16">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C17">
+        <v>49</v>
+      </c>
+      <c r="D17">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C18">
+        <v>62</v>
+      </c>
+      <c r="D18">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C19">
+        <v>19</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C21">
+        <v>27</v>
+      </c>
+      <c r="D21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C22">
+        <v>55</v>
+      </c>
+      <c r="D22">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C23">
+        <v>57</v>
+      </c>
+      <c r="D23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C24">
+        <v>31</v>
+      </c>
+      <c r="D24">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C25">
+        <v>43</v>
+      </c>
+      <c r="D25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>1</v>
       </c>
       <c r="B28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C28">
+        <v>16</v>
+      </c>
+      <c r="D28">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C29">
+        <v>53</v>
+      </c>
+      <c r="D29">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C30">
+        <v>68</v>
+      </c>
+      <c r="D30">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>1</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C31">
+        <v>33</v>
+      </c>
+      <c r="D31">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C32">
+        <v>15</v>
+      </c>
+      <c r="D32">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C34">
+        <v>25</v>
+      </c>
+      <c r="D34">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>1</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C35">
+        <v>35</v>
+      </c>
+      <c r="D35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>1</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C36">
+        <v>23</v>
+      </c>
+      <c r="D36">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>1</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C37">
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>1</v>
       </c>
       <c r="B38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C38">
+        <v>29</v>
+      </c>
+      <c r="D38">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>1</v>
       </c>
       <c r="B39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C39">
+        <v>9</v>
+      </c>
+      <c r="D39">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>1</v>
       </c>
       <c r="B40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C40">
+        <v>6</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>1</v>
       </c>
       <c r="B41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C41">
+        <v>60</v>
+      </c>
+      <c r="D41">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>1</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C42">
+        <v>69</v>
+      </c>
+      <c r="D42">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>1</v>
       </c>
       <c r="B43">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C43">
+        <v>56</v>
+      </c>
+      <c r="D43">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>1</v>
       </c>
       <c r="B44">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C44">
+        <v>36</v>
+      </c>
+      <c r="D44">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>1</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C45">
+        <v>5</v>
+      </c>
+      <c r="D45">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>1</v>
       </c>
       <c r="B46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C46">
+        <v>41</v>
+      </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>1</v>
       </c>
       <c r="B47">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C47">
+        <v>50</v>
+      </c>
+      <c r="D47">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>1</v>
       </c>
       <c r="B48">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C48">
+        <v>26</v>
+      </c>
+      <c r="D48">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>1</v>
       </c>
       <c r="B49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C49">
+        <v>54</v>
+      </c>
+      <c r="D49" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>1</v>
       </c>
       <c r="B50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C50">
+        <v>39</v>
+      </c>
+      <c r="D50">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>1</v>
       </c>
       <c r="B51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C51">
+        <v>28</v>
+      </c>
+      <c r="D51">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>1</v>
       </c>
       <c r="B52">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C52">
+        <v>50</v>
+      </c>
+      <c r="D52">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>1</v>
       </c>
       <c r="B53">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C53">
+        <v>29</v>
+      </c>
+      <c r="D53">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>1</v>
       </c>
       <c r="B54">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C54">
+        <v>37</v>
+      </c>
+      <c r="D54">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>1</v>
       </c>
       <c r="B55">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C55">
+        <v>8</v>
+      </c>
+      <c r="D55">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>1</v>
       </c>
       <c r="B56">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C56">
+        <v>49</v>
+      </c>
+      <c r="D56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>1</v>
       </c>
       <c r="B57">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C57">
+        <v>61</v>
+      </c>
+      <c r="D57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>1</v>
       </c>
       <c r="B58">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C58">
+        <v>43</v>
+      </c>
+      <c r="D58">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>1</v>
       </c>
       <c r="B59">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C59">
+        <v>55</v>
+      </c>
+      <c r="D59">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>1</v>
       </c>
       <c r="B60">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C60">
+        <v>35</v>
+      </c>
+      <c r="D60">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>1</v>
       </c>
       <c r="B61">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C61">
+        <v>6</v>
+      </c>
+      <c r="D61">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>1</v>
       </c>
       <c r="B62">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C62">
+        <v>10</v>
+      </c>
+      <c r="D62">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>1</v>
       </c>
       <c r="B63">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C63">
+        <v>14</v>
+      </c>
+      <c r="D63">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>1</v>
       </c>
       <c r="B64">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C64">
+        <v>39</v>
+      </c>
+      <c r="D64">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>1</v>
       </c>
       <c r="B65">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C65">
+        <v>16</v>
+      </c>
+      <c r="D65">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>1</v>
       </c>
       <c r="B66">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C66">
+        <v>46</v>
+      </c>
+      <c r="D66">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>1</v>
       </c>
       <c r="B67">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C67">
+        <v>12</v>
+      </c>
+      <c r="D67">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>1</v>
       </c>
       <c r="B68">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C68">
+        <v>53</v>
+      </c>
+      <c r="D68">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>1</v>
       </c>
       <c r="B69">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C69">
+        <v>65</v>
+      </c>
+      <c r="D69">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>1</v>
       </c>
       <c r="B70">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C70">
+        <v>57</v>
+      </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>1</v>
       </c>
       <c r="B71">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C71">
+        <v>41</v>
+      </c>
+      <c r="D71">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>1</v>
       </c>
       <c r="B72">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C72">
+        <v>20</v>
+      </c>
+      <c r="D72">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>1</v>
       </c>
       <c r="B73">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C73">
+        <v>52</v>
+      </c>
+      <c r="D73">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>1</v>
       </c>
       <c r="B74">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C74">
+        <v>56</v>
+      </c>
+      <c r="D74">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>1</v>
       </c>
       <c r="B75">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C75">
+        <v>22</v>
+      </c>
+      <c r="D75">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>1</v>
       </c>
       <c r="B76">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C76">
+        <v>9</v>
+      </c>
+      <c r="D76">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>1</v>
       </c>
       <c r="B77">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C77">
+        <v>45</v>
+      </c>
+      <c r="D77">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>1</v>
       </c>
       <c r="B78">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C78">
+        <v>10</v>
+      </c>
+      <c r="D78">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>1</v>
       </c>
       <c r="B79">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C79">
+        <v>63</v>
+      </c>
+      <c r="D79">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>1</v>
       </c>
       <c r="B80">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C80">
+        <v>49</v>
+      </c>
+      <c r="D80">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>1</v>
       </c>
       <c r="B81">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C81">
+        <v>48</v>
+      </c>
+      <c r="D81">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
         <v>1</v>
       </c>
       <c r="B82">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C82">
+        <v>27</v>
+      </c>
+      <c r="D82">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A83">
         <v>1</v>
       </c>
       <c r="B83">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C83">
+        <v>15</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A84">
         <v>1</v>
       </c>
       <c r="B84">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C84">
+        <v>37</v>
+      </c>
+      <c r="D84">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A85">
         <v>1</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C85">
+        <v>17</v>
+      </c>
+      <c r="D85">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A86">
         <v>1</v>
       </c>
       <c r="B86">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C86">
+        <v>18</v>
+      </c>
+      <c r="D86">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A87">
         <v>1</v>
       </c>
       <c r="B87">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C87">
+        <v>31</v>
+      </c>
+      <c r="D87">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A88">
         <v>1</v>
       </c>
       <c r="B88">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C88">
+        <v>53</v>
+      </c>
+      <c r="D88">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A89">
         <v>1</v>
       </c>
       <c r="B89">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C89">
+        <v>52</v>
+      </c>
+      <c r="D89">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A90">
         <v>1</v>
       </c>
       <c r="B90">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C90">
+        <v>46</v>
+      </c>
+      <c r="D90">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A91">
         <v>1</v>
       </c>
       <c r="B91">
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C91">
+        <v>64</v>
+      </c>
+      <c r="D91">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A92">
         <v>1</v>
       </c>
       <c r="B92">
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C92">
+        <v>4</v>
+      </c>
+      <c r="D92">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A93">
         <v>1</v>
       </c>
       <c r="B93">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A94">
         <v>1</v>
       </c>
       <c r="B94">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C94">
+        <v>43</v>
+      </c>
+      <c r="D94">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A95">
         <v>1</v>
       </c>
       <c r="B95">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C95">
+        <v>25</v>
+      </c>
+      <c r="D95">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A96">
         <v>1</v>
       </c>
       <c r="B96">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C96">
+        <v>57</v>
+      </c>
+      <c r="D96">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A97">
         <v>1</v>
       </c>
       <c r="B97">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C97">
+        <v>8</v>
+      </c>
+      <c r="D97">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A98">
         <v>1</v>
       </c>
       <c r="B98">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C98">
+        <v>19</v>
+      </c>
+      <c r="D98">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A99">
         <v>1</v>
       </c>
       <c r="B99">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C99">
+        <v>21</v>
+      </c>
+      <c r="D99">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A100">
         <v>1</v>
       </c>
       <c r="B100">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A101">
         <v>1</v>
       </c>
       <c r="B101">
         <v>100</v>
+      </c>
+      <c r="C101">
+        <v>59</v>
+      </c>
+      <c r="D101">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -4117,6 +4729,12 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>33</v>
+      </c>
+      <c r="D2">
+        <v>39</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
@@ -4125,6 +4743,12 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>36</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
@@ -4133,6 +4757,12 @@
       <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
@@ -4141,6 +4771,12 @@
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5">
+        <v>28</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
@@ -4149,6 +4785,12 @@
       <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6">
+        <v>56</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
@@ -4157,6 +4799,12 @@
       <c r="B7">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>67</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
@@ -4165,6 +4813,12 @@
       <c r="B8">
         <v>7</v>
       </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>35</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
@@ -4173,6 +4827,12 @@
       <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9">
+        <v>55</v>
+      </c>
+      <c r="D9">
+        <v>16</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
@@ -4181,6 +4841,12 @@
       <c r="B10">
         <v>9</v>
       </c>
+      <c r="C10">
+        <v>27</v>
+      </c>
+      <c r="D10">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
@@ -4189,6 +4855,12 @@
       <c r="B11">
         <v>10</v>
       </c>
+      <c r="C11">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>48</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
@@ -4197,6 +4869,12 @@
       <c r="B12">
         <v>11</v>
       </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
@@ -4205,6 +4883,12 @@
       <c r="B13">
         <v>12</v>
       </c>
+      <c r="C13">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>69</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
@@ -4213,6 +4897,12 @@
       <c r="B14">
         <v>13</v>
       </c>
+      <c r="C14">
+        <v>49</v>
+      </c>
+      <c r="D14">
+        <v>57</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
@@ -4221,6 +4911,12 @@
       <c r="B15">
         <v>14</v>
       </c>
+      <c r="C15">
+        <v>30</v>
+      </c>
+      <c r="D15">
+        <v>52</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
@@ -4229,690 +4925,1207 @@
       <c r="B16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C16">
+        <v>19</v>
+      </c>
+      <c r="D16">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C17">
+        <v>41</v>
+      </c>
+      <c r="D17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C18">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C19">
+        <v>52</v>
+      </c>
+      <c r="D19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C20">
+        <v>35</v>
+      </c>
+      <c r="D20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C21">
+        <v>24</v>
+      </c>
+      <c r="D21">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C22">
+        <v>46</v>
+      </c>
+      <c r="D22">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C23">
+        <v>31</v>
+      </c>
+      <c r="D23">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C24">
+        <v>18</v>
+      </c>
+      <c r="D24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C25">
+        <v>32</v>
+      </c>
+      <c r="D25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C26">
+        <v>50</v>
+      </c>
+      <c r="D26">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C27">
+        <v>29</v>
+      </c>
+      <c r="D27">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>1</v>
       </c>
       <c r="B28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C29">
+        <v>70</v>
+      </c>
+      <c r="D29">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C30">
+        <v>53</v>
+      </c>
+      <c r="D30">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>1</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C31">
+        <v>45</v>
+      </c>
+      <c r="D31">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C32">
+        <v>9</v>
+      </c>
+      <c r="D32">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C33">
+        <v>22</v>
+      </c>
+      <c r="D33">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>1</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C35">
+        <v>15</v>
+      </c>
+      <c r="D35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>1</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C36">
+        <v>39</v>
+      </c>
+      <c r="D36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>1</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C37">
+        <v>59</v>
+      </c>
+      <c r="D37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>1</v>
       </c>
       <c r="B38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C38">
+        <v>20</v>
+      </c>
+      <c r="D38">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>1</v>
       </c>
       <c r="B39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C39">
+        <v>62</v>
+      </c>
+      <c r="D39">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>1</v>
       </c>
       <c r="B40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C40">
+        <v>37</v>
+      </c>
+      <c r="D40">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>1</v>
       </c>
       <c r="B41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C41">
+        <v>36</v>
+      </c>
+      <c r="D41">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>1</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C42">
+        <v>3</v>
+      </c>
+      <c r="D42">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>1</v>
       </c>
       <c r="B43">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C43">
+        <v>28</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>1</v>
       </c>
       <c r="B44">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C44">
+        <v>57</v>
+      </c>
+      <c r="D44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>1</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>1</v>
       </c>
       <c r="B46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C46">
+        <v>26</v>
+      </c>
+      <c r="D46">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>1</v>
       </c>
       <c r="B47">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C47" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>1</v>
       </c>
       <c r="B48">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C48">
+        <v>27</v>
+      </c>
+      <c r="D48">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>1</v>
       </c>
       <c r="B49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C49">
+        <v>12</v>
+      </c>
+      <c r="D49">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>1</v>
       </c>
       <c r="B50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C50">
+        <v>10</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>1</v>
       </c>
       <c r="B51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C51">
+        <v>8</v>
+      </c>
+      <c r="D51">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>1</v>
       </c>
       <c r="B52">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C52">
+        <v>43</v>
+      </c>
+      <c r="D52">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>1</v>
       </c>
       <c r="B53">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C53">
+        <v>25</v>
+      </c>
+      <c r="D53">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>1</v>
       </c>
       <c r="B54">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C54">
+        <v>33</v>
+      </c>
+      <c r="D54">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>1</v>
       </c>
       <c r="B55">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C55">
+        <v>61</v>
+      </c>
+      <c r="D55">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>1</v>
       </c>
       <c r="B56">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C56">
+        <v>56</v>
+      </c>
+      <c r="D56">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>1</v>
       </c>
       <c r="B57">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C57">
+        <v>41</v>
+      </c>
+      <c r="D57">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>1</v>
       </c>
       <c r="B58">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C58">
+        <v>9</v>
+      </c>
+      <c r="D58">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>1</v>
       </c>
       <c r="B59">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C59">
+        <v>48</v>
+      </c>
+      <c r="D59">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>1</v>
       </c>
       <c r="B60">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C60">
+        <v>4</v>
+      </c>
+      <c r="D60">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>1</v>
       </c>
       <c r="B61">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C61">
+        <v>16</v>
+      </c>
+      <c r="D61">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>1</v>
       </c>
       <c r="B62">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C62">
+        <v>46</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>1</v>
       </c>
       <c r="B63">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C63">
+        <v>68</v>
+      </c>
+      <c r="D63">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>1</v>
       </c>
       <c r="B64">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C64">
+        <v>60</v>
+      </c>
+      <c r="D64">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>1</v>
       </c>
       <c r="B65">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C65">
+        <v>59</v>
+      </c>
+      <c r="D65">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>1</v>
       </c>
       <c r="B66">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C66">
+        <v>18</v>
+      </c>
+      <c r="D66">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>1</v>
       </c>
       <c r="B67">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C67">
+        <v>29</v>
+      </c>
+      <c r="D67">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>1</v>
       </c>
       <c r="B68">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>1</v>
       </c>
       <c r="B69">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C69">
+        <v>23</v>
+      </c>
+      <c r="D69">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>1</v>
       </c>
       <c r="B70">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C70">
+        <v>39</v>
+      </c>
+      <c r="D70">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>1</v>
       </c>
       <c r="B71">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C71">
+        <v>13</v>
+      </c>
+      <c r="D71">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>1</v>
       </c>
       <c r="B72">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C72">
+        <v>37</v>
+      </c>
+      <c r="D72">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>1</v>
       </c>
       <c r="B73">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C73">
+        <v>15</v>
+      </c>
+      <c r="D73">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>1</v>
       </c>
       <c r="B74">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C74">
+        <v>49</v>
+      </c>
+      <c r="D74">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>1</v>
       </c>
       <c r="B75">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C75">
+        <v>64</v>
+      </c>
+      <c r="D75">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>1</v>
       </c>
       <c r="B76">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C76">
+        <v>19</v>
+      </c>
+      <c r="D76">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>1</v>
       </c>
       <c r="B77">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C77">
+        <v>31</v>
+      </c>
+      <c r="D77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>1</v>
       </c>
       <c r="B78">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C78">
+        <v>5</v>
+      </c>
+      <c r="D78">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>1</v>
       </c>
       <c r="B79">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C79">
+        <v>65</v>
+      </c>
+      <c r="D79">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>1</v>
       </c>
       <c r="B80">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C80">
+        <v>57</v>
+      </c>
+      <c r="D80">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>1</v>
       </c>
       <c r="B81">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C81">
+        <v>52</v>
+      </c>
+      <c r="D81">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
         <v>1</v>
       </c>
       <c r="B82">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C82">
+        <v>35</v>
+      </c>
+      <c r="D82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A83">
         <v>1</v>
       </c>
       <c r="B83">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C83">
+        <v>38</v>
+      </c>
+      <c r="D83">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A84">
         <v>1</v>
       </c>
       <c r="B84">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C84">
+        <v>50</v>
+      </c>
+      <c r="D84">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A85">
         <v>1</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C85">
+        <v>48</v>
+      </c>
+      <c r="D85">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A86">
         <v>1</v>
       </c>
       <c r="B86">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C86">
+        <v>10</v>
+      </c>
+      <c r="D86">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A87">
         <v>1</v>
       </c>
       <c r="B87">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C87">
+        <v>45</v>
+      </c>
+      <c r="D87">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A88">
         <v>1</v>
       </c>
       <c r="B88">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C88">
+        <v>60</v>
+      </c>
+      <c r="D88">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A89">
         <v>1</v>
       </c>
       <c r="B89">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C89">
+        <v>16</v>
+      </c>
+      <c r="D89">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A90">
         <v>1</v>
       </c>
       <c r="B90">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C90">
+        <v>20</v>
+      </c>
+      <c r="D90">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A91">
         <v>1</v>
       </c>
       <c r="B91">
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C91">
+        <v>34</v>
+      </c>
+      <c r="D91">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A92">
         <v>1</v>
       </c>
       <c r="B92">
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C92">
+        <v>26</v>
+      </c>
+      <c r="D92">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A93">
         <v>1</v>
       </c>
       <c r="B93">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C93">
+        <v>6</v>
+      </c>
+      <c r="D93">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A94">
         <v>1</v>
       </c>
       <c r="B94">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C94">
+        <v>18</v>
+      </c>
+      <c r="D94">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A95">
         <v>1</v>
       </c>
       <c r="B95">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C95">
+        <v>36</v>
+      </c>
+      <c r="D95">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A96">
         <v>1</v>
       </c>
       <c r="B96">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C96">
+        <v>53</v>
+      </c>
+      <c r="D96">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A97">
         <v>1</v>
       </c>
       <c r="B97">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C97">
+        <v>69</v>
+      </c>
+      <c r="D97">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A98">
         <v>1</v>
       </c>
       <c r="B98">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C98">
+        <v>43</v>
+      </c>
+      <c r="D98">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A99">
         <v>1</v>
       </c>
       <c r="B99">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C99">
+        <v>25</v>
+      </c>
+      <c r="D99">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A100">
         <v>1</v>
       </c>
       <c r="B100">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C100">
+        <v>5</v>
+      </c>
+      <c r="D100">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A101">
         <v>1</v>
       </c>
       <c r="B101">
         <v>100</v>
+      </c>
+      <c r="C101">
+        <v>55</v>
+      </c>
+      <c r="D101">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4942,6 +6155,12 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>46</v>
+      </c>
+      <c r="D2">
+        <v>49</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
@@ -4950,6 +6169,12 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>59</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
@@ -4958,6 +6183,12 @@
       <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>39</v>
+      </c>
+      <c r="D4">
+        <v>26</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
@@ -4966,6 +6197,12 @@
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5">
+        <v>65</v>
+      </c>
+      <c r="D5">
+        <v>36</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
@@ -4974,6 +6211,12 @@
       <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>35</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
@@ -4982,6 +6225,12 @@
       <c r="B7">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>48</v>
+      </c>
+      <c r="D7">
+        <v>68</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
@@ -4990,6 +6239,12 @@
       <c r="B8">
         <v>7</v>
       </c>
+      <c r="C8">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>60</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
@@ -4998,6 +6253,12 @@
       <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
@@ -5006,6 +6267,12 @@
       <c r="B10">
         <v>9</v>
       </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>18</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
@@ -5014,6 +6281,12 @@
       <c r="B11">
         <v>10</v>
       </c>
+      <c r="C11">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>52</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
@@ -5022,6 +6295,12 @@
       <c r="B12">
         <v>11</v>
       </c>
+      <c r="C12">
+        <v>35</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
@@ -5030,6 +6309,12 @@
       <c r="B13">
         <v>12</v>
       </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>33</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
@@ -5038,6 +6323,12 @@
       <c r="B14">
         <v>13</v>
       </c>
+      <c r="C14">
+        <v>18</v>
+      </c>
+      <c r="D14">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
@@ -5046,6 +6337,12 @@
       <c r="B15">
         <v>14</v>
       </c>
+      <c r="C15">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>25</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
@@ -5054,690 +6351,1207 @@
       <c r="B16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C16">
+        <v>43</v>
+      </c>
+      <c r="D16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C17">
+        <v>64</v>
+      </c>
+      <c r="D17">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C18">
+        <v>27</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C20">
+        <v>49</v>
+      </c>
+      <c r="D20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C21">
+        <v>12</v>
+      </c>
+      <c r="D21">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C23">
+        <v>14</v>
+      </c>
+      <c r="D23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C24">
+        <v>60</v>
+      </c>
+      <c r="D24">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C25">
+        <v>52</v>
+      </c>
+      <c r="D25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C26">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C27">
+        <v>70</v>
+      </c>
+      <c r="D27">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>1</v>
       </c>
       <c r="B28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C28">
+        <v>26</v>
+      </c>
+      <c r="D28">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C29">
+        <v>45</v>
+      </c>
+      <c r="D29">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C30">
+        <v>53</v>
+      </c>
+      <c r="D30">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>1</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C31">
+        <v>6</v>
+      </c>
+      <c r="D31">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C32">
+        <v>50</v>
+      </c>
+      <c r="D32">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C34">
+        <v>33</v>
+      </c>
+      <c r="D34">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>1</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C35">
+        <v>55</v>
+      </c>
+      <c r="D35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>1</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C36">
+        <v>19</v>
+      </c>
+      <c r="D36">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>1</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C37">
+        <v>36</v>
+      </c>
+      <c r="D37">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>1</v>
       </c>
       <c r="B38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C38">
+        <v>39</v>
+      </c>
+      <c r="D38">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>1</v>
       </c>
       <c r="B39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C39">
+        <v>62</v>
+      </c>
+      <c r="D39">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>1</v>
       </c>
       <c r="B40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C40">
+        <v>57</v>
+      </c>
+      <c r="D40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>1</v>
       </c>
       <c r="B41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C41">
+        <v>31</v>
+      </c>
+      <c r="D41">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>1</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C42">
+        <v>37</v>
+      </c>
+      <c r="D42">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>1</v>
       </c>
       <c r="B43">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C43">
+        <v>41</v>
+      </c>
+      <c r="D43">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>1</v>
       </c>
       <c r="B44">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C44">
+        <v>46</v>
+      </c>
+      <c r="D44">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>1</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C45">
+        <v>69</v>
+      </c>
+      <c r="D45">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>1</v>
       </c>
       <c r="B46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>1</v>
       </c>
       <c r="B47">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C47">
+        <v>59</v>
+      </c>
+      <c r="D47">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>1</v>
       </c>
       <c r="B48">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C48">
+        <v>9</v>
+      </c>
+      <c r="D48">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>1</v>
       </c>
       <c r="B49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C49">
+        <v>25</v>
+      </c>
+      <c r="D49">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>1</v>
       </c>
       <c r="B50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C50">
+        <v>49</v>
+      </c>
+      <c r="D50">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>1</v>
       </c>
       <c r="B51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C51">
+        <v>29</v>
+      </c>
+      <c r="D51">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>1</v>
       </c>
       <c r="B52">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C52">
+        <v>5</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>1</v>
       </c>
       <c r="B53">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C53">
+        <v>13</v>
+      </c>
+      <c r="D53">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>1</v>
       </c>
       <c r="B54">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C54">
+        <v>43</v>
+      </c>
+      <c r="D54">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>1</v>
       </c>
       <c r="B55">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C55">
+        <v>38</v>
+      </c>
+      <c r="D55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>1</v>
       </c>
       <c r="B56">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C56">
+        <v>35</v>
+      </c>
+      <c r="D56">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>1</v>
       </c>
       <c r="B57">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>1</v>
       </c>
       <c r="B58">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C58">
+        <v>60</v>
+      </c>
+      <c r="D58">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>1</v>
       </c>
       <c r="B59">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C59">
+        <v>15</v>
+      </c>
+      <c r="D59">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>1</v>
       </c>
       <c r="B60">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C60">
+        <v>20</v>
+      </c>
+      <c r="D60">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>1</v>
       </c>
       <c r="B61">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>1</v>
       </c>
       <c r="B62">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C62">
+        <v>56</v>
+      </c>
+      <c r="D62">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>1</v>
       </c>
       <c r="B63">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C63">
+        <v>12</v>
+      </c>
+      <c r="D63">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>1</v>
       </c>
       <c r="B64">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C64">
+        <v>53</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>1</v>
       </c>
       <c r="B65">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C65">
+        <v>48</v>
+      </c>
+      <c r="D65">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>1</v>
       </c>
       <c r="B66">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C66">
+        <v>26</v>
+      </c>
+      <c r="D66">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>1</v>
       </c>
       <c r="B67">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C67">
+        <v>63</v>
+      </c>
+      <c r="D67">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>1</v>
       </c>
       <c r="B68">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C68">
+        <v>18</v>
+      </c>
+      <c r="D68">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>1</v>
       </c>
       <c r="B69">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C69">
+        <v>6</v>
+      </c>
+      <c r="D69">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>1</v>
       </c>
       <c r="B70">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C70">
+        <v>46</v>
+      </c>
+      <c r="D70">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>1</v>
       </c>
       <c r="B71">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C71">
+        <v>8</v>
+      </c>
+      <c r="D71">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>1</v>
       </c>
       <c r="B72">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C72">
+        <v>27</v>
+      </c>
+      <c r="D72">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>1</v>
       </c>
       <c r="B73">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C73">
+        <v>34</v>
+      </c>
+      <c r="D73">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>1</v>
       </c>
       <c r="B74">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C74">
+        <v>10</v>
+      </c>
+      <c r="D74">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>1</v>
       </c>
       <c r="B75">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C75">
+        <v>25</v>
+      </c>
+      <c r="D75">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>1</v>
       </c>
       <c r="B76">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C76">
+        <v>50</v>
+      </c>
+      <c r="D76">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>1</v>
       </c>
       <c r="B77">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C77">
+        <v>36</v>
+      </c>
+      <c r="D77">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>1</v>
       </c>
       <c r="B78">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C78">
+        <v>37</v>
+      </c>
+      <c r="D78">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>1</v>
       </c>
       <c r="B79">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C79">
+        <v>31</v>
+      </c>
+      <c r="D79">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>1</v>
       </c>
       <c r="B80">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C80">
+        <v>3</v>
+      </c>
+      <c r="D80">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>1</v>
       </c>
       <c r="B81">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C81">
+        <v>66</v>
+      </c>
+      <c r="D81">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
         <v>1</v>
       </c>
       <c r="B82">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C82">
+        <v>57</v>
+      </c>
+      <c r="D82">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A83">
         <v>1</v>
       </c>
       <c r="B83">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C83">
+        <v>41</v>
+      </c>
+      <c r="D83">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A84">
         <v>1</v>
       </c>
       <c r="B84">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C84">
+        <v>43</v>
+      </c>
+      <c r="D84">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A85">
         <v>1</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C85">
+        <v>52</v>
+      </c>
+      <c r="D85">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A86">
         <v>1</v>
       </c>
       <c r="B86">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C86">
+        <v>39</v>
+      </c>
+      <c r="D86">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A87">
         <v>1</v>
       </c>
       <c r="B87">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C87">
+        <v>47</v>
+      </c>
+      <c r="D87">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A88">
         <v>1</v>
       </c>
       <c r="B88">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C88">
+        <v>35</v>
+      </c>
+      <c r="D88">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A89">
         <v>1</v>
       </c>
       <c r="B89">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C89">
+        <v>55</v>
+      </c>
+      <c r="D89">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A90">
         <v>1</v>
       </c>
       <c r="B90">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C90">
+        <v>5</v>
+      </c>
+      <c r="D90">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A91">
         <v>1</v>
       </c>
       <c r="B91">
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C91">
+        <v>29</v>
+      </c>
+      <c r="D91">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A92">
         <v>1</v>
       </c>
       <c r="B92">
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C92">
+        <v>19</v>
+      </c>
+      <c r="D92">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A93">
         <v>1</v>
       </c>
       <c r="B93">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C93">
+        <v>42</v>
+      </c>
+      <c r="D93">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A94">
         <v>1</v>
       </c>
       <c r="B94">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C94">
+        <v>49</v>
+      </c>
+      <c r="D94">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A95">
         <v>1</v>
       </c>
       <c r="B95">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C95">
+        <v>13</v>
+      </c>
+      <c r="D95">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A96">
         <v>1</v>
       </c>
       <c r="B96">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C96">
+        <v>33</v>
+      </c>
+      <c r="D96">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A97">
         <v>1</v>
       </c>
       <c r="B97">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C97">
+        <v>28</v>
+      </c>
+      <c r="D97">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A98">
         <v>1</v>
       </c>
       <c r="B98">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C98">
+        <v>56</v>
+      </c>
+      <c r="D98">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A99">
         <v>1</v>
       </c>
       <c r="B99">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C99">
+        <v>68</v>
+      </c>
+      <c r="D99">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A100">
         <v>1</v>
       </c>
       <c r="B100">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C100">
+        <v>4</v>
+      </c>
+      <c r="D100">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A101">
         <v>1</v>
       </c>
       <c r="B101">
         <v>100</v>
+      </c>
+      <c r="C101">
+        <v>45</v>
+      </c>
+      <c r="D101">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5767,6 +7581,12 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>53</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
@@ -5775,6 +7595,12 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>31</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
@@ -5783,6 +7609,12 @@
       <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>27</v>
+      </c>
+      <c r="D4">
+        <v>46</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
@@ -5791,6 +7623,12 @@
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5">
+        <v>70</v>
+      </c>
+      <c r="D5">
+        <v>45</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
@@ -5799,6 +7637,12 @@
       <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6">
+        <v>43</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
@@ -5807,6 +7651,12 @@
       <c r="B7">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
@@ -5815,6 +7665,12 @@
       <c r="B8">
         <v>7</v>
       </c>
+      <c r="C8">
+        <v>18</v>
+      </c>
+      <c r="D8">
+        <v>35</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
@@ -5823,6 +7679,12 @@
       <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9">
+        <v>55</v>
+      </c>
+      <c r="D9">
+        <v>25</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
@@ -5831,6 +7693,12 @@
       <c r="B10">
         <v>9</v>
       </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
@@ -5839,6 +7707,12 @@
       <c r="B11">
         <v>10</v>
       </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
@@ -5847,6 +7721,12 @@
       <c r="B12">
         <v>11</v>
       </c>
+      <c r="C12">
+        <v>33</v>
+      </c>
+      <c r="D12">
+        <v>60</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
@@ -5855,6 +7735,12 @@
       <c r="B13">
         <v>12</v>
       </c>
+      <c r="C13">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>66</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
@@ -5863,6 +7749,12 @@
       <c r="B14">
         <v>13</v>
       </c>
+      <c r="C14">
+        <v>57</v>
+      </c>
+      <c r="D14">
+        <v>43</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
@@ -5871,6 +7763,12 @@
       <c r="B15">
         <v>14</v>
       </c>
+      <c r="C15">
+        <v>52</v>
+      </c>
+      <c r="D15">
+        <v>59</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
@@ -5879,685 +7777,1201 @@
       <c r="B16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C17">
+        <v>69</v>
+      </c>
+      <c r="D17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C18">
+        <v>50</v>
+      </c>
+      <c r="D18">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C19">
+        <v>36</v>
+      </c>
+      <c r="D19">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C20">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C21">
+        <v>24</v>
+      </c>
+      <c r="D21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C22">
+        <v>35</v>
+      </c>
+      <c r="D22">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C23">
+        <v>16</v>
+      </c>
+      <c r="D23">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C25">
+        <v>31</v>
+      </c>
+      <c r="D25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C26">
+        <v>46</v>
+      </c>
+      <c r="D26">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C27">
+        <v>12</v>
+      </c>
+      <c r="D27">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>1</v>
       </c>
       <c r="B28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C28">
+        <v>26</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C29">
+        <v>68</v>
+      </c>
+      <c r="D29">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C30">
+        <v>49</v>
+      </c>
+      <c r="D30">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>1</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C31">
+        <v>6</v>
+      </c>
+      <c r="D31">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C32">
+        <v>19</v>
+      </c>
+      <c r="D32">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C33">
+        <v>41</v>
+      </c>
+      <c r="D33">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C34">
+        <v>43</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>1</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C35">
+        <v>17</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>1</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C36">
+        <v>20</v>
+      </c>
+      <c r="D36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>1</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C37">
+        <v>8</v>
+      </c>
+      <c r="D37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>1</v>
       </c>
       <c r="B38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C38">
+        <v>5</v>
+      </c>
+      <c r="D38">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>1</v>
       </c>
       <c r="B39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C39">
+        <v>29</v>
+      </c>
+      <c r="D39">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>1</v>
       </c>
       <c r="B40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C40">
+        <v>39</v>
+      </c>
+      <c r="D40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>1</v>
       </c>
       <c r="B41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C41">
+        <v>64</v>
+      </c>
+      <c r="D41">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>1</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C42">
+        <v>37</v>
+      </c>
+      <c r="D42">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>1</v>
       </c>
       <c r="B43">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C43">
+        <v>59</v>
+      </c>
+      <c r="D43">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>1</v>
       </c>
       <c r="B44">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>1</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>1</v>
       </c>
       <c r="B46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C46">
+        <v>56</v>
+      </c>
+      <c r="D46">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>1</v>
       </c>
       <c r="B47">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C47">
+        <v>30</v>
+      </c>
+      <c r="D47">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>1</v>
       </c>
       <c r="B48">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C48">
+        <v>27</v>
+      </c>
+      <c r="D48">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>1</v>
       </c>
       <c r="B49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C49">
+        <v>12</v>
+      </c>
+      <c r="D49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>1</v>
       </c>
       <c r="B50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C50">
+        <v>33</v>
+      </c>
+      <c r="D50">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>1</v>
       </c>
       <c r="B51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C51">
+        <v>28</v>
+      </c>
+      <c r="D51">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>1</v>
       </c>
       <c r="B52">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C52">
+        <v>10</v>
+      </c>
+      <c r="D52">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>1</v>
       </c>
       <c r="B53">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C53">
+        <v>15</v>
+      </c>
+      <c r="D53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>1</v>
       </c>
       <c r="B54">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C54">
+        <v>60</v>
+      </c>
+      <c r="D54">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>1</v>
       </c>
       <c r="B55">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C55">
+        <v>65</v>
+      </c>
+      <c r="D55">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>1</v>
       </c>
       <c r="B56">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C56">
+        <v>35</v>
+      </c>
+      <c r="D56">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>1</v>
       </c>
       <c r="B57">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C57">
+        <v>13</v>
+      </c>
+      <c r="D57">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>1</v>
       </c>
       <c r="B58">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C58">
+        <v>50</v>
+      </c>
+      <c r="D58">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>1</v>
       </c>
       <c r="B59">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C59">
+        <v>48</v>
+      </c>
+      <c r="D59">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>1</v>
       </c>
       <c r="B60">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C60">
+        <v>9</v>
+      </c>
+      <c r="D60">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>1</v>
       </c>
       <c r="B61">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C61">
+        <v>36</v>
+      </c>
+      <c r="D61">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>1</v>
       </c>
       <c r="B62">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C62">
+        <v>53</v>
+      </c>
+      <c r="D62">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>1</v>
       </c>
       <c r="B63">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C63">
+        <v>67</v>
+      </c>
+      <c r="D63">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>1</v>
       </c>
       <c r="B64">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C64">
+        <v>18</v>
+      </c>
+      <c r="D64">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>1</v>
       </c>
       <c r="B65">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C65">
+        <v>31</v>
+      </c>
+      <c r="D65">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>1</v>
       </c>
       <c r="B66">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C66">
+        <v>19</v>
+      </c>
+      <c r="D66">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>1</v>
       </c>
       <c r="B67">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C67">
+        <v>6</v>
+      </c>
+      <c r="D67">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>1</v>
       </c>
       <c r="B68">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C68">
+        <v>49</v>
+      </c>
+      <c r="D68">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>1</v>
       </c>
       <c r="B69">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C69" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>1</v>
       </c>
       <c r="B70">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C70">
+        <v>33</v>
+      </c>
+      <c r="D70">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>1</v>
       </c>
       <c r="B71">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C71">
+        <v>55</v>
+      </c>
+      <c r="D71">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>1</v>
       </c>
       <c r="B72">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C72">
+        <v>57</v>
+      </c>
+      <c r="D72">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>1</v>
       </c>
       <c r="B73">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C73">
+        <v>63</v>
+      </c>
+      <c r="D73">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>1</v>
       </c>
       <c r="B74">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C74">
+        <v>26</v>
+      </c>
+      <c r="D74">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>1</v>
       </c>
       <c r="B75">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C75">
+        <v>2</v>
+      </c>
+      <c r="D75">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>1</v>
       </c>
       <c r="B76">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C76">
+        <v>46</v>
+      </c>
+      <c r="D76">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>1</v>
       </c>
       <c r="B77">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C77">
+        <v>52</v>
+      </c>
+      <c r="D77">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>1</v>
       </c>
       <c r="B78">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C78">
+        <v>20</v>
+      </c>
+      <c r="D78">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>1</v>
       </c>
       <c r="B79">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C79">
+        <v>22</v>
+      </c>
+      <c r="D79">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>1</v>
       </c>
       <c r="B80">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C80">
+        <v>39</v>
+      </c>
+      <c r="D80">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>1</v>
       </c>
       <c r="B81">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C81">
+        <v>48</v>
+      </c>
+      <c r="D81">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
         <v>1</v>
       </c>
       <c r="B82">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C82">
+        <v>4</v>
+      </c>
+      <c r="D82">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A83">
         <v>1</v>
       </c>
       <c r="B83">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C83">
+        <v>29</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A84">
         <v>1</v>
       </c>
       <c r="B84">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C84">
+        <v>56</v>
+      </c>
+      <c r="D84">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A85">
         <v>1</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C85">
+        <v>23</v>
+      </c>
+      <c r="D85">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A86">
         <v>1</v>
       </c>
       <c r="B86">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C86">
+        <v>60</v>
+      </c>
+      <c r="D86">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A87">
         <v>1</v>
       </c>
       <c r="B87">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C87">
+        <v>8</v>
+      </c>
+      <c r="D87">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A88">
         <v>1</v>
       </c>
       <c r="B88">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C88">
+        <v>3</v>
+      </c>
+      <c r="D88">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A89">
         <v>1</v>
       </c>
       <c r="B89">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C89">
+        <v>25</v>
+      </c>
+      <c r="D89">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A90">
         <v>1</v>
       </c>
       <c r="B90">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C90">
+        <v>37</v>
+      </c>
+      <c r="D90">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A91">
         <v>1</v>
       </c>
       <c r="B91">
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C91">
+        <v>61</v>
+      </c>
+      <c r="D91">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A92">
         <v>1</v>
       </c>
       <c r="B92">
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C92">
+        <v>19</v>
+      </c>
+      <c r="D92">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A93">
         <v>1</v>
       </c>
       <c r="B93">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C93">
+        <v>59</v>
+      </c>
+      <c r="D93">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A94">
         <v>1</v>
       </c>
       <c r="B94">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C94">
+        <v>5</v>
+      </c>
+      <c r="D94">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A95">
         <v>1</v>
       </c>
       <c r="B95">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C95">
+        <v>45</v>
+      </c>
+      <c r="D95">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A96">
         <v>1</v>
       </c>
       <c r="B96">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C96">
+        <v>53</v>
+      </c>
+      <c r="D96">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A97">
         <v>1</v>
       </c>
       <c r="B97">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C97">
+        <v>32</v>
+      </c>
+      <c r="D97">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A98">
         <v>1</v>
       </c>
       <c r="B98">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C98">
+        <v>26</v>
+      </c>
+      <c r="D98">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A99">
         <v>1</v>
       </c>
       <c r="B99">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C99">
+        <v>13</v>
+      </c>
+      <c r="D99">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A100">
         <v>1</v>
       </c>
       <c r="B100">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C100">
+        <v>10</v>
+      </c>
+      <c r="D100">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A101">
         <v>1</v>
       </c>
       <c r="B101">
         <v>100</v>
+      </c>
+      <c r="C101">
+        <v>28</v>
+      </c>
+      <c r="D101">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
